--- a/fix-fhirpath-valueCodeableConcept/ig/StructureDefinition-tddui-task-bilan.xlsx
+++ b/fix-fhirpath-valueCodeableConcept/ig/StructureDefinition-tddui-task-bilan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:42:47+00:00</t>
+    <t>2026-07-01T08:54:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-fhirpath-valueCodeableConcept/ig/StructureDefinition-tddui-task-bilan.xlsx
+++ b/fix-fhirpath-valueCodeableConcept/ig/StructureDefinition-tddui-task-bilan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T08:54:05+00:00</t>
+    <t>2026-07-01T10:22:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix-fhirpath-valueCodeableConcept/ig/StructureDefinition-tddui-task-bilan.xlsx
+++ b/fix-fhirpath-valueCodeableConcept/ig/StructureDefinition-tddui-task-bilan.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T10:22:46+00:00</t>
+    <t>2026-07-01T11:17:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
